--- a/data/trans_orig/Q23-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q23-Habitat-trans_orig.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,75; 16,19</t>
+          <t>15,76; 16,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,92; 16,56</t>
+          <t>15,91; 16,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,02; 16,77</t>
+          <t>15,96; 16,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,64; 17,47</t>
+          <t>16,6; 17,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,16; 18,31</t>
+          <t>17,1; 18,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,35; 18,77</t>
+          <t>17,28; 18,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,1; 16,52</t>
+          <t>16,08; 16,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,43; 17,03</t>
+          <t>16,41; 17,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,61; 17,33</t>
+          <t>16,59; 17,34</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,29; 16,99</t>
+          <t>16,31; 17,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,28; 16,85</t>
+          <t>16,28; 16,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,22; 16,95</t>
+          <t>16,25; 16,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,12; 18,02</t>
+          <t>17,14; 18,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,27; 18,18</t>
+          <t>17,2; 18,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,88; 17,68</t>
+          <t>16,9; 17,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,64; 17,22</t>
+          <t>16,65; 17,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,73; 17,27</t>
+          <t>16,73; 17,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,61; 17,15</t>
+          <t>16,6; 17,17</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,03; 16,58</t>
+          <t>16,01; 16,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,15; 16,83</t>
+          <t>16,14; 16,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,18; 16,79</t>
+          <t>16,16; 16,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,33; 19,04</t>
+          <t>17,31; 18,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,86; 17,93</t>
+          <t>16,84; 17,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,22; 18,33</t>
+          <t>17,18; 18,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,57; 17,31</t>
+          <t>16,59; 17,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,53; 17,12</t>
+          <t>16,54; 17,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,69; 17,26</t>
+          <t>16,72; 17,28</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,15; 16,61</t>
+          <t>16,16; 16,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,29; 16,8</t>
+          <t>16,29; 16,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,2; 16,93</t>
+          <t>16,22; 16,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,96; 17,93</t>
+          <t>16,97; 17,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,41; 18,75</t>
+          <t>17,41; 18,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,38; 18,35</t>
+          <t>17,4; 18,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,56; 17,05</t>
+          <t>16,57; 17,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,84; 17,52</t>
+          <t>16,83; 17,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,87; 17,45</t>
+          <t>16,83; 17,45</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,19; 16,51</t>
+          <t>16,19; 16,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,32; 16,6</t>
+          <t>16,31; 16,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,31; 16,67</t>
+          <t>16,3; 16,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,21; 17,74</t>
+          <t>17,2; 17,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,41; 17,97</t>
+          <t>17,38; 17,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,39; 17,92</t>
+          <t>17,41; 17,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,64; 16,91</t>
+          <t>16,62; 16,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>16,77; 17,07</t>
+          <t>16,79; 17,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,83; 17,12</t>
+          <t>16,81; 17,13</t>
         </is>
       </c>
     </row>
